--- a/instructions/Ir-9/Ir-9-pytania.xlsx
+++ b/instructions/Ir-9/Ir-9-pytania.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:I192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,11 @@
           <t>Explanation</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -499,6 +504,9 @@
           <t>Ir-9 § 11 ust. 12</t>
         </is>
       </c>
+      <c r="I2" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -541,6 +549,9 @@
           <t>Ir-9 § 1 ust. 2</t>
         </is>
       </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -583,6 +594,9 @@
           <t>Ir-9 § 11 ust. 1 pkt 5 i pkt 7</t>
         </is>
       </c>
+      <c r="I4" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -625,6 +639,9 @@
           <t>Ir-9 § 12 ust. 12</t>
         </is>
       </c>
+      <c r="I5" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -667,6 +684,9 @@
           <t>Ir-9 § 20 ust. 2 pkt 1</t>
         </is>
       </c>
+      <c r="I6" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -709,6 +729,9 @@
           <t>Ir-9 § 20 ust. 2 pkt 3</t>
         </is>
       </c>
+      <c r="I7" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -751,6 +774,9 @@
           <t>Ir-9 § 20 ust. 4 pkt 1</t>
         </is>
       </c>
+      <c r="I8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -793,6 +819,9 @@
           <t>Ir-9 § 20 ust. 9</t>
         </is>
       </c>
+      <c r="I9" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -835,6 +864,9 @@
           <t>Ir-9 § 21 ust. 2 pkt 21</t>
         </is>
       </c>
+      <c r="I10" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -877,6 +909,9 @@
           <t>Ir-9 § 26 ust. 5</t>
         </is>
       </c>
+      <c r="I11" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -919,6 +954,9 @@
           <t>Ir-9 § 26 ust. 4</t>
         </is>
       </c>
+      <c r="I12" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -961,6 +999,9 @@
           <t>Ir-9 § 26 ust. 5</t>
         </is>
       </c>
+      <c r="I13" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1003,6 +1044,9 @@
           <t>Ir-9 § 26 ust. 1</t>
         </is>
       </c>
+      <c r="I14" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1045,6 +1089,9 @@
           <t>Ir-9 § 26 ust. 2</t>
         </is>
       </c>
+      <c r="I15" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1087,6 +1134,9 @@
           <t>Ir-9 § 26 ust. 6</t>
         </is>
       </c>
+      <c r="I16" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1255,6 +1305,9 @@
           <t>Ir-9 § 4 ust. 3</t>
         </is>
       </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1297,6 +1350,9 @@
           <t>Ir-9 § 7 ust. 4 pkt 2</t>
         </is>
       </c>
+      <c r="I21" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1339,6 +1395,9 @@
           <t>Ir-9 § 8 ust. 3</t>
         </is>
       </c>
+      <c r="I22" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1381,6 +1440,9 @@
           <t>Ir-9 § 8 ust. 6 pkt 4</t>
         </is>
       </c>
+      <c r="I23" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1423,6 +1485,9 @@
           <t>Ir-9 § 9 ust. 4</t>
         </is>
       </c>
+      <c r="I24" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1465,6 +1530,9 @@
           <t>Ir-9 § 10 ust. 2</t>
         </is>
       </c>
+      <c r="I25" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1507,6 +1575,9 @@
           <t>Ir-9 § 10 ust. 5</t>
         </is>
       </c>
+      <c r="I26" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1549,6 +1620,9 @@
           <t>Ir-9 § 10 ust. 5</t>
         </is>
       </c>
+      <c r="I27" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1591,6 +1665,9 @@
           <t>Ir-9 § 10 ust. 9</t>
         </is>
       </c>
+      <c r="I28" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1633,6 +1710,9 @@
           <t>Ir-9 § 10 ust. 10</t>
         </is>
       </c>
+      <c r="I29" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1675,6 +1755,9 @@
           <t>Ir-9 § 10 ust. 13</t>
         </is>
       </c>
+      <c r="I30" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1717,6 +1800,9 @@
           <t>Ir-9 § 10 ust. 20</t>
         </is>
       </c>
+      <c r="I31" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1759,6 +1845,9 @@
           <t>Ir-9 § 10 ust. 28</t>
         </is>
       </c>
+      <c r="I32" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1801,6 +1890,9 @@
           <t>Ir-9 § 11 ust. 1 pkt 2</t>
         </is>
       </c>
+      <c r="I33" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1843,6 +1935,9 @@
           <t>Ir-9 § 11 ust. 1 pkt 3</t>
         </is>
       </c>
+      <c r="I34" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1885,6 +1980,9 @@
           <t>Ir-9 § 11 ust. 1 pkt 4</t>
         </is>
       </c>
+      <c r="I35" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1927,6 +2025,9 @@
           <t>Ir-9 § 11 ust. 8 pkt 2</t>
         </is>
       </c>
+      <c r="I36" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1969,6 +2070,9 @@
           <t>Ir-9 § 11 ust. 8 pkt 3</t>
         </is>
       </c>
+      <c r="I37" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2011,6 +2115,9 @@
           <t>Ir-9 § 11 ust. 9</t>
         </is>
       </c>
+      <c r="I38" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2053,6 +2160,9 @@
           <t>Ir-9 § 11 ust. 12 pkt 2</t>
         </is>
       </c>
+      <c r="I39" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2095,6 +2205,9 @@
           <t>Ir-9 § 11 ust. 13</t>
         </is>
       </c>
+      <c r="I40" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2137,6 +2250,9 @@
           <t>Ir-9 § 11 ust. 15 pkt 3</t>
         </is>
       </c>
+      <c r="I41" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2179,6 +2295,9 @@
           <t>Ir-9 § 12 ust. 5</t>
         </is>
       </c>
+      <c r="I42" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2221,6 +2340,9 @@
           <t>Ir-9 § 12 ust. 1</t>
         </is>
       </c>
+      <c r="I43" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2263,6 +2385,9 @@
           <t>Ir-9 § 12 ust. 9</t>
         </is>
       </c>
+      <c r="I44" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2305,6 +2430,9 @@
           <t>Ir-9 § 12 ust. 15</t>
         </is>
       </c>
+      <c r="I45" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2347,6 +2475,9 @@
           <t>Ir-9 § 12 ust. 11</t>
         </is>
       </c>
+      <c r="I46" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2389,6 +2520,9 @@
           <t>Ir-9 § 13 ust. 5</t>
         </is>
       </c>
+      <c r="I47" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2431,6 +2565,9 @@
           <t>Ir-9 § 13 ust. 7</t>
         </is>
       </c>
+      <c r="I48" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2473,6 +2610,9 @@
           <t>Ir-9 § 13 ust. 8</t>
         </is>
       </c>
+      <c r="I49" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2515,6 +2655,9 @@
           <t>Ir-9 § 13 ust. 3</t>
         </is>
       </c>
+      <c r="I50" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2557,6 +2700,9 @@
           <t>Ir-9 § 14 ust. 5 pkt 2</t>
         </is>
       </c>
+      <c r="I51" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2599,6 +2745,9 @@
           <t>Ir-9 § 14 ust. 3 pkt 1</t>
         </is>
       </c>
+      <c r="I52" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2641,6 +2790,9 @@
           <t>Ir-9 § 14 ust. 6</t>
         </is>
       </c>
+      <c r="I53" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2683,6 +2835,9 @@
           <t>Ir-9 § 15 ust. 2</t>
         </is>
       </c>
+      <c r="I54" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2725,6 +2880,9 @@
           <t>Ir-9 § 15 ust. 6</t>
         </is>
       </c>
+      <c r="I55" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2767,6 +2925,9 @@
           <t>Ir-9 § 15 ust. 4</t>
         </is>
       </c>
+      <c r="I56" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2809,6 +2970,9 @@
           <t>Ir-9 § 15 ust. 8</t>
         </is>
       </c>
+      <c r="I57" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2851,6 +3015,9 @@
           <t>Ir-9 § 15 ust. 9</t>
         </is>
       </c>
+      <c r="I58" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2893,6 +3060,9 @@
           <t>Ir-9 § 16 ust. 2</t>
         </is>
       </c>
+      <c r="I59" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2935,6 +3105,9 @@
           <t>Ir-9 § 18 ust. 5</t>
         </is>
       </c>
+      <c r="I60" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2977,6 +3150,9 @@
           <t>Ir-9 § 19 ust. 3 pkt 6 lit. a</t>
         </is>
       </c>
+      <c r="I61" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3019,6 +3195,9 @@
           <t>Ir-9 § 19 ust. 5</t>
         </is>
       </c>
+      <c r="I62" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3061,6 +3240,9 @@
           <t>Ir-9 § 20 ust. 2 pkt 2</t>
         </is>
       </c>
+      <c r="I63" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3103,6 +3285,9 @@
           <t>Ir-9 § 20 ust. 2 pkt 2</t>
         </is>
       </c>
+      <c r="I64" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3145,6 +3330,9 @@
           <t>Ir-9 § 20 ust. 7 pkt 5</t>
         </is>
       </c>
+      <c r="I65" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3187,6 +3375,9 @@
           <t>Ir-9 § 20 ust. 11</t>
         </is>
       </c>
+      <c r="I66" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3229,6 +3420,9 @@
           <t>Ir-9 § 20 ust. 1</t>
         </is>
       </c>
+      <c r="I67" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3271,6 +3465,9 @@
           <t>Ir-9 § 20 ust. 10</t>
         </is>
       </c>
+      <c r="I68" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3313,6 +3510,9 @@
           <t>Ir-9 § 21 ust. 2 pkt 4a</t>
         </is>
       </c>
+      <c r="I69" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3355,6 +3555,9 @@
           <t>Ir-9 § 21 ust. 2 pkt 6</t>
         </is>
       </c>
+      <c r="I70" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3397,6 +3600,9 @@
           <t>Ir-9 § 21 ust. 2 pkt 20</t>
         </is>
       </c>
+      <c r="I71" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3439,6 +3645,9 @@
           <t>Ir-9 § 21 ust. 2 pkt 21</t>
         </is>
       </c>
+      <c r="I72" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3481,6 +3690,9 @@
           <t>Ir-9 § 21 ust. 2 pkt 9</t>
         </is>
       </c>
+      <c r="I73" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3523,6 +3735,9 @@
           <t>Ir-9 § 21 ust. 2 pkt 7</t>
         </is>
       </c>
+      <c r="I74" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3565,6 +3780,9 @@
           <t>Ir-9 § 22 ust. 4</t>
         </is>
       </c>
+      <c r="I75" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3607,6 +3825,9 @@
           <t>Ir-9 § 22 ust. 5 pkt 1</t>
         </is>
       </c>
+      <c r="I76" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3649,6 +3870,9 @@
           <t>Ir-9 § 24 ust. 6</t>
         </is>
       </c>
+      <c r="I77" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3691,6 +3915,9 @@
           <t>Ir-9 § 25 ust. 3</t>
         </is>
       </c>
+      <c r="I78" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3733,6 +3960,9 @@
           <t>Ir-9 § 25 ust. 2 pkt 2</t>
         </is>
       </c>
+      <c r="I79" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4195,6 +4425,9 @@
           <t>Ir-9 § 4 ust. 4</t>
         </is>
       </c>
+      <c r="I90" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4237,6 +4470,9 @@
           <t>Ir-9 § 5 ust. 5</t>
         </is>
       </c>
+      <c r="I91" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4279,6 +4515,9 @@
           <t>Ir-9 § 5 ust. 7</t>
         </is>
       </c>
+      <c r="I92" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4321,6 +4560,9 @@
           <t>Ir-9 § 5 ust. 6</t>
         </is>
       </c>
+      <c r="I93" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4363,6 +4605,9 @@
           <t>Ir-9 § 6 ust. 4</t>
         </is>
       </c>
+      <c r="I94" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4405,6 +4650,9 @@
           <t>Ir-9 § 6 ust. 3</t>
         </is>
       </c>
+      <c r="I95" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4447,6 +4695,9 @@
           <t>Ir-9 § 7 ust. 2 pkt 5</t>
         </is>
       </c>
+      <c r="I96" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4489,6 +4740,9 @@
           <t>Ir-9 § 7 ust. 3 pkt 9 lit. c</t>
         </is>
       </c>
+      <c r="I97" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4531,6 +4785,9 @@
           <t>Ir-9 § 7 ust. 4 pkt 2</t>
         </is>
       </c>
+      <c r="I98" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4573,6 +4830,9 @@
           <t>Ir-9 § 7 ust. 5</t>
         </is>
       </c>
+      <c r="I99" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4615,6 +4875,9 @@
           <t>Ir-9 § 7 ust. 6</t>
         </is>
       </c>
+      <c r="I100" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4657,6 +4920,9 @@
           <t>Ir-9 § 7 ust. 7</t>
         </is>
       </c>
+      <c r="I101" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4699,6 +4965,9 @@
           <t>Ir-9 § 7 ust. 9</t>
         </is>
       </c>
+      <c r="I102" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4741,6 +5010,9 @@
           <t>Ir-9 § 8 ust. 1</t>
         </is>
       </c>
+      <c r="I103" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4783,6 +5055,9 @@
           <t>Ir-9 § 8 ust. 2</t>
         </is>
       </c>
+      <c r="I104" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4825,6 +5100,9 @@
           <t>Ir-9 § 8 ust. 3</t>
         </is>
       </c>
+      <c r="I105" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4867,6 +5145,9 @@
           <t>Ir-9 § 8 ust. 6</t>
         </is>
       </c>
+      <c r="I106" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4909,6 +5190,9 @@
           <t>Ir-9 § 8 ust. 8</t>
         </is>
       </c>
+      <c r="I107" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4951,6 +5235,9 @@
           <t>Ir-9 § 8 ust. 7</t>
         </is>
       </c>
+      <c r="I108" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4993,6 +5280,9 @@
           <t>Ir-9 § 9 ust. 2</t>
         </is>
       </c>
+      <c r="I109" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5035,6 +5325,9 @@
           <t>Ir-9 § 9 ust. 5</t>
         </is>
       </c>
+      <c r="I110" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5077,6 +5370,9 @@
           <t>Ir-9 § 9 ust. 8</t>
         </is>
       </c>
+      <c r="I111" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5119,6 +5415,9 @@
           <t>Ir-9 § 10 ust. 27 pkt 2</t>
         </is>
       </c>
+      <c r="I112" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5161,6 +5460,9 @@
           <t>Ir-9 § 10 ust. 4</t>
         </is>
       </c>
+      <c r="I113" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5203,6 +5505,9 @@
           <t>Ir-9 § 10 ust. 25</t>
         </is>
       </c>
+      <c r="I114" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5245,6 +5550,9 @@
           <t>Ir-9 § 10 ust. 27 pkt 5</t>
         </is>
       </c>
+      <c r="I115" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5287,6 +5595,9 @@
           <t>Ir-9 § 11 ust. 15 pkt 1</t>
         </is>
       </c>
+      <c r="I116" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5329,6 +5640,9 @@
           <t>Ir-9 § 12 ust. 10</t>
         </is>
       </c>
+      <c r="I117" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5371,6 +5685,9 @@
           <t>Ir-9 § 13 ust. 9</t>
         </is>
       </c>
+      <c r="I118" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5413,6 +5730,9 @@
           <t>Ir-9 § 15 ust. 3</t>
         </is>
       </c>
+      <c r="I119" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5455,6 +5775,9 @@
           <t>Ir-9 § 15 ust. 7</t>
         </is>
       </c>
+      <c r="I120" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5497,6 +5820,9 @@
           <t>Ir-9 § 19 ust. 3 pkt 2</t>
         </is>
       </c>
+      <c r="I121" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5539,6 +5865,9 @@
           <t>Ir-9 § 19 ust. 3 pkt 3</t>
         </is>
       </c>
+      <c r="I122" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5581,6 +5910,9 @@
           <t>Ir-9 § 19 ust. 3 pkt 7</t>
         </is>
       </c>
+      <c r="I123" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5623,6 +5955,9 @@
           <t>Ir-9 § 10 ust. 1</t>
         </is>
       </c>
+      <c r="I124" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5665,6 +6000,9 @@
           <t>Ir-9 § 10 ust. 27 pkt 1</t>
         </is>
       </c>
+      <c r="I125" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5707,6 +6045,9 @@
           <t>Ir-9 § 10 ust. 27 pkt 2</t>
         </is>
       </c>
+      <c r="I126" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5749,6 +6090,9 @@
           <t>Ir-9 § 10 ust. 3</t>
         </is>
       </c>
+      <c r="I127" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5791,6 +6135,9 @@
           <t>Ir-9 § 10 ust. 7</t>
         </is>
       </c>
+      <c r="I128" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5833,6 +6180,9 @@
           <t>Ir-9 § 10 ust. 6</t>
         </is>
       </c>
+      <c r="I129" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5875,6 +6225,9 @@
           <t>Ir-9 § 10 ust. 8</t>
         </is>
       </c>
+      <c r="I130" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5917,6 +6270,9 @@
           <t>Ir-9 § 10 ust. 27</t>
         </is>
       </c>
+      <c r="I131" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5959,6 +6315,9 @@
           <t>Ir-9 § 10 ust. 27 pkt 4 lit. a</t>
         </is>
       </c>
+      <c r="I132" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6001,6 +6360,9 @@
           <t>Ir-9 § 10 ust. 27 pkt 8 lit. b</t>
         </is>
       </c>
+      <c r="I133" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6043,6 +6405,9 @@
           <t>Ir-9 § 10 ust. 21</t>
         </is>
       </c>
+      <c r="I134" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6085,6 +6450,9 @@
           <t>Ir-9 § 11 ust. 3</t>
         </is>
       </c>
+      <c r="I135" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6127,6 +6495,9 @@
           <t>Ir-9 § 11 ust. 8 pkt 1 i pkt 11</t>
         </is>
       </c>
+      <c r="I136" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6169,6 +6540,9 @@
           <t>Ir-9 § 11 ust. 16 pkt 1</t>
         </is>
       </c>
+      <c r="I137" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6211,6 +6585,9 @@
           <t>Ir-9 § 11 ust. 17</t>
         </is>
       </c>
+      <c r="I138" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6253,6 +6630,9 @@
           <t>Ir-9 § 12 ust. 13</t>
         </is>
       </c>
+      <c r="I139" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6295,6 +6675,9 @@
           <t>Ir-9 § 13 ust. 2</t>
         </is>
       </c>
+      <c r="I140" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6337,6 +6720,9 @@
           <t>Ir-9 § 13 ust. 6</t>
         </is>
       </c>
+      <c r="I141" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6379,6 +6765,9 @@
           <t>Ir-9 § 13 ust. 4</t>
         </is>
       </c>
+      <c r="I142" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6421,6 +6810,9 @@
           <t>Ir-9 § 14 ust. 2</t>
         </is>
       </c>
+      <c r="I143" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6463,6 +6855,9 @@
           <t>Ir-9 § 14 ust. 5 pkt 2</t>
         </is>
       </c>
+      <c r="I144" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6505,6 +6900,9 @@
           <t>Ir-9 § 15 ust. 1</t>
         </is>
       </c>
+      <c r="I145" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6547,6 +6945,9 @@
           <t>Ir-9 § 15 ust. 5</t>
         </is>
       </c>
+      <c r="I146" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6589,6 +6990,9 @@
           <t>Ir-9 § 15 ust. 4</t>
         </is>
       </c>
+      <c r="I147" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6631,6 +7035,9 @@
           <t>Ir-9 § 16 ust. 1 pkt 1</t>
         </is>
       </c>
+      <c r="I148" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6673,6 +7080,9 @@
           <t>Ir-9 § 17 ust. 2</t>
         </is>
       </c>
+      <c r="I149" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6715,6 +7125,9 @@
           <t>Ir-9 § 17 ust. 5</t>
         </is>
       </c>
+      <c r="I150" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6757,6 +7170,9 @@
           <t>Ir-9 § 17 ust. 3</t>
         </is>
       </c>
+      <c r="I151" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6799,6 +7215,9 @@
           <t>Ir-9 § 18 ust. 2 pkt 1</t>
         </is>
       </c>
+      <c r="I152" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6841,6 +7260,9 @@
           <t>Ir-9 § 18 ust. 4</t>
         </is>
       </c>
+      <c r="I153" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6883,6 +7305,9 @@
           <t>Ir-9 § 2 ust. 1</t>
         </is>
       </c>
+      <c r="I154" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6925,6 +7350,9 @@
           <t>Ir-9 § 2 ust. 2</t>
         </is>
       </c>
+      <c r="I155" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6967,6 +7395,9 @@
           <t>Ir-9 § 2 ust. 3 i ust. 4</t>
         </is>
       </c>
+      <c r="I156" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7009,6 +7440,9 @@
           <t>Ir-9 § 2 ust. 5</t>
         </is>
       </c>
+      <c r="I157" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7051,6 +7485,9 @@
           <t>Ir-9 § 2 ust. 7</t>
         </is>
       </c>
+      <c r="I158" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7093,6 +7530,9 @@
           <t>Ir-9 § 2 ust. 16</t>
         </is>
       </c>
+      <c r="I159" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7135,6 +7575,9 @@
           <t>Ir-9 § 2 ust. 20</t>
         </is>
       </c>
+      <c r="I160" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7177,6 +7620,9 @@
           <t>Ir-9 § 2 ust. 11</t>
         </is>
       </c>
+      <c r="I161" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7219,6 +7665,9 @@
           <t>Ir-9 § 21 ust. 2 pkt 4b</t>
         </is>
       </c>
+      <c r="I162" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7261,6 +7710,9 @@
           <t>Ir-9 § 21 ust. 2 pkt 22</t>
         </is>
       </c>
+      <c r="I163" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7303,6 +7755,9 @@
           <t>Ir-9 § 22 ust. 5 pkt 2</t>
         </is>
       </c>
+      <c r="I164" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7345,6 +7800,9 @@
           <t>Ir-9 § 23 ust. 2 pkt 1</t>
         </is>
       </c>
+      <c r="I165" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7387,6 +7845,9 @@
           <t>Ir-9 § 23 ust. 3</t>
         </is>
       </c>
+      <c r="I166" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7429,6 +7890,9 @@
           <t>Ir-9 § 24 ust. 3</t>
         </is>
       </c>
+      <c r="I167" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7471,6 +7935,9 @@
           <t>Ir-9 § 24 ust. 8</t>
         </is>
       </c>
+      <c r="I168" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7513,6 +7980,9 @@
           <t>Ir-9 § 7 ust. 8</t>
         </is>
       </c>
+      <c r="I169" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7555,6 +8025,9 @@
           <t>Ir-9 § 7 ust. 2 pkt 6</t>
         </is>
       </c>
+      <c r="I170" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7597,6 +8070,9 @@
           <t>Ir-9 § 11 ust. 4 pkt 1</t>
         </is>
       </c>
+      <c r="I171" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7639,6 +8115,9 @@
           <t>Ir-9 § 11 ust. 4 pkt 2</t>
         </is>
       </c>
+      <c r="I172" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7681,6 +8160,9 @@
           <t>Ir-9 § 11 ust. 4 pkt 3</t>
         </is>
       </c>
+      <c r="I173" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7723,6 +8205,9 @@
           <t>Ir-9 § 11 ust. 4 pkt 4</t>
         </is>
       </c>
+      <c r="I174" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7765,6 +8250,9 @@
           <t>Ir-9 § 11 ust. 4 pkt 5</t>
         </is>
       </c>
+      <c r="I175" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7807,6 +8295,9 @@
           <t>Ir-9 § 11 ust. 4 pkt 6</t>
         </is>
       </c>
+      <c r="I176" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7849,6 +8340,9 @@
           <t>Ir-9 § 11 ust. 3 pkt 1</t>
         </is>
       </c>
+      <c r="I177" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7891,6 +8385,9 @@
           <t>Ir-9 § 11 ust. 3 pkt 2</t>
         </is>
       </c>
+      <c r="I178" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7933,6 +8430,9 @@
           <t>Ir-9 § 11 ust. 3 pkt 3</t>
         </is>
       </c>
+      <c r="I179" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7975,6 +8475,9 @@
           <t>Ir-9 § 12 ust. 8</t>
         </is>
       </c>
+      <c r="I180" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8017,6 +8520,9 @@
           <t>Ir-9 § 12 ust. 8</t>
         </is>
       </c>
+      <c r="I181" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8059,6 +8565,9 @@
           <t>Ir-9 § 12 ust. 8</t>
         </is>
       </c>
+      <c r="I182" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8101,6 +8610,9 @@
           <t>Ir-9 § 3 ust. 1</t>
         </is>
       </c>
+      <c r="I183" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8143,6 +8655,9 @@
           <t>Ir-9 § 3 ust. 1</t>
         </is>
       </c>
+      <c r="I184" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8185,6 +8700,9 @@
           <t>Ir-9 § 3 ust. 1</t>
         </is>
       </c>
+      <c r="I185" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8227,6 +8745,9 @@
           <t>Ir-9 § 3 ust. 1</t>
         </is>
       </c>
+      <c r="I186" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8269,6 +8790,9 @@
           <t>Ir-9 § 6 ust. 2 pkt 1</t>
         </is>
       </c>
+      <c r="I187" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8311,6 +8835,9 @@
           <t>Ir-9 § 6 ust. 2 pkt 2</t>
         </is>
       </c>
+      <c r="I188" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8353,6 +8880,9 @@
           <t>Ir-9 § 6 ust. 2 pkt 3</t>
         </is>
       </c>
+      <c r="I189" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8395,6 +8925,9 @@
           <t>Ir-9 § 8 ust. 5 pkt 1</t>
         </is>
       </c>
+      <c r="I190" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8437,6 +8970,9 @@
           <t>Ir-9 § 8 ust. 5 pkt 2</t>
         </is>
       </c>
+      <c r="I191" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8478,6 +9014,9 @@
         <is>
           <t>Ir-9 § 8 ust. 5 pkt 3</t>
         </is>
+      </c>
+      <c r="I192" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
